--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.12478516216803</v>
+        <v>1.970277588852306</v>
       </c>
       <c r="D2" t="n">
-        <v>11.77520964572066</v>
+        <v>1.913471567429607</v>
       </c>
       <c r="E2" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F2" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.71833254540708</v>
+        <v>4.341729038628651</v>
       </c>
       <c r="D3" t="n">
-        <v>26.19636538629831</v>
+        <v>4.256909375273477</v>
       </c>
       <c r="E3" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F3" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.10782113405225</v>
+        <v>2.29252093428349</v>
       </c>
       <c r="D4" t="n">
-        <v>20.260120375149</v>
+        <v>3.292269560961713</v>
       </c>
       <c r="E4" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F4" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.26478024826368</v>
+        <v>3.780526790342849</v>
       </c>
       <c r="D5" t="n">
-        <v>13.20037878244409</v>
+        <v>2.145061552147164</v>
       </c>
       <c r="E5" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F5" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.74493316587088</v>
+        <v>2.883551639454018</v>
       </c>
       <c r="D6" t="n">
-        <v>51.45258626716357</v>
+        <v>8.361045268414081</v>
       </c>
       <c r="E6" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F6" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.88142027674514</v>
+        <v>1.768230794971085</v>
       </c>
       <c r="D7" t="n">
-        <v>13.2065977922365</v>
+        <v>2.14607214123843</v>
       </c>
       <c r="E7" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F7" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.77235810733551</v>
+        <v>3.213008192442021</v>
       </c>
       <c r="D8" t="n">
-        <v>61.46729807333905</v>
+        <v>9.988435936917597</v>
       </c>
       <c r="E8" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F8" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.30407146587784</v>
+        <v>5.574411613205149</v>
       </c>
       <c r="D9" t="n">
-        <v>35.55189095801178</v>
+        <v>5.777182280676914</v>
       </c>
       <c r="E9" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F9" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.29583279634485</v>
+        <v>4.110572829406038</v>
       </c>
       <c r="D10" t="n">
-        <v>58.72746581299045</v>
+        <v>9.543213194610949</v>
       </c>
       <c r="E10" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F10" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.26592528959348</v>
+        <v>2.48071285955894</v>
       </c>
       <c r="D11" t="n">
-        <v>15.15891800379266</v>
+        <v>2.463324175616308</v>
       </c>
       <c r="E11" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F11" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.28628996385861</v>
+        <v>9.634022119127025</v>
       </c>
       <c r="D12" t="n">
-        <v>60.7926576850531</v>
+        <v>9.878806873821128</v>
       </c>
       <c r="E12" t="n">
-        <v>13.15181025951829</v>
+        <v>2.137169167171721</v>
       </c>
       <c r="F12" t="n">
-        <v>19.88795835720667</v>
+        <v>3.231793233046083</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
